--- a/Result/profitability/4989.xlsx
+++ b/Result/profitability/4989.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM53"/>
+  <dimension ref="A1:AM54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.53</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.7374999999999999</v>
+        <v>-0.7224999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>-9.776249999999999</v>
+        <v>-8.341249999999999</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.77</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.5262499999999999</v>
+        <v>-0.48875</v>
       </c>
       <c r="N3" t="n">
-        <v>-7.01</v>
+        <v>-4.799999999999999</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>2.55</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.06999999999999995</v>
+        <v>-0.08749999999999991</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.018749999999999</v>
+        <v>-1.62</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>1.99</v>
       </c>
       <c r="M5" t="n">
-        <v>0.26125</v>
+        <v>0.3900000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1949999999999997</v>
+        <v>2.305000000000001</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -7161,6 +7161,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>4989</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>1073</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1114</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-41</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-3.85</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-117</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>-10.90%</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>-0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>-117</v>
+      </c>
+      <c r="K54" t="n">
+        <v>-111</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="M54" t="n">
+        <v>-0.7712499999999999</v>
+      </c>
+      <c r="N54" t="n">
+        <v>-11.0375</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W54" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="X54" t="n">
+        <v>-7.153846153846154</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>-8.779999999999999</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>-1.780933062880325</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>-0.5628415300546448</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>20</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>-0.8385744234800838</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK54" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
